--- a/output/pdf_financials_xlsx/V.xlsx
+++ b/output/pdf_financials_xlsx/V.xlsx
@@ -715,16 +715,16 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>0.02055</v>
+        <v>-0.02055</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>0.125694</v>
+        <v>-0.125694</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>0.001151</v>
+        <v>-0.001151</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>0.004757</v>
+        <v>-0.004757</v>
       </c>
     </row>
     <row r="17">
@@ -807,16 +807,16 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>0.02055</v>
+        <v>-0.02055</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>0.125694</v>
+        <v>-0.125694</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>0.001151</v>
+        <v>-0.001151</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>0.004757</v>
+        <v>-0.004757</v>
       </c>
     </row>
     <row r="21">
@@ -864,16 +864,16 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>0.02055</v>
+        <v>-0.02055</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>0.125694</v>
+        <v>-0.125694</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>0.001151</v>
+        <v>-0.001151</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>0.004757</v>
+        <v>-0.004757</v>
       </c>
     </row>
     <row r="24">
@@ -921,7 +921,7 @@
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>0.3425</v>
+        <v>-0.3425</v>
       </c>
       <c r="C26" s="1" t="inlineStr">
         <is>
@@ -946,16 +946,16 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>0.02055</v>
+        <v>-0.02055</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>0.125694</v>
+        <v>-0.125694</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>0.001151</v>
+        <v>-0.001151</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>0.004757</v>
+        <v>-0.004757</v>
       </c>
     </row>
     <row r="28">
@@ -984,16 +984,16 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>0.02055</v>
+        <v>-0.02055</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>0.125694</v>
+        <v>-0.125694</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>0.001151</v>
+        <v>-0.001151</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>0.004757</v>
+        <v>-0.004757</v>
       </c>
     </row>
     <row r="30">
@@ -1030,16 +1030,16 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="32">
@@ -2354,7 +2354,7 @@
         </is>
       </c>
       <c r="B99" s="3" t="n">
-        <v>0.02055</v>
+        <v>-0.02055</v>
       </c>
       <c r="C99" s="3" t="n">
         <v>-0.125694</v>
@@ -4605,13 +4605,13 @@
         </is>
       </c>
       <c r="F44" s="5" t="n">
-        <v>0.125694</v>
+        <v>-0.125694</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>0.001151</v>
+        <v>-0.001151</v>
       </c>
       <c r="H44" s="5" t="n">
-        <v>0.004757</v>
+        <v>-0.004757</v>
       </c>
     </row>
     <row r="45">
@@ -5368,10 +5368,10 @@
         </is>
       </c>
       <c r="E66" s="5" t="n">
-        <v>0.02055</v>
+        <v>-0.02055</v>
       </c>
       <c r="F66" s="5" t="n">
-        <v>0.125694</v>
+        <v>-0.125694</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/V.xlsx
+++ b/output/pdf_financials_xlsx/V.xlsx
@@ -601,16 +601,16 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0</v>
+        <v>0.02055</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0</v>
+        <v>0.143375</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0</v>
+        <v>0.025053</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>0</v>
+        <v>0.023954</v>
       </c>
     </row>
     <row r="11">
@@ -620,16 +620,16 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>0</v>
+        <v>-0.02055</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>0</v>
+        <v>-0.143375</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>0</v>
+        <v>-0.025053</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>0</v>
+        <v>-0.023954</v>
       </c>
     </row>
     <row r="12">
@@ -642,13 +642,13 @@
         <v>0</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>-0.017681</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>-0.023902</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>-0.019197</v>
       </c>
     </row>
     <row r="13">
@@ -949,13 +949,13 @@
         <v>-0.02055</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.125694</v>
+        <v>-0.108013</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-0.001151</v>
+        <v>0.022751</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-0.004757</v>
+        <v>0.01444</v>
       </c>
     </row>
     <row r="28">
@@ -987,13 +987,13 @@
         <v>-0.02055</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.125694</v>
+        <v>-0.108013</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-0.001151</v>
+        <v>0.022751</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-0.004757</v>
+        <v>0.01444</v>
       </c>
     </row>
     <row r="30">
@@ -4526,7 +4526,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E42" s="5" t="n">
@@ -4560,7 +4560,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
